--- a/artfynd/A 14556-2021 artfynd.xlsx
+++ b/artfynd/A 14556-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118365376</v>
+        <v>118365373</v>
       </c>
       <c r="B2" t="n">
-        <v>96801</v>
+        <v>78484</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -782,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118365373</v>
+        <v>118365376</v>
       </c>
       <c r="B3" t="n">
-        <v>78484</v>
+        <v>96801</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,30 +793,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>

--- a/artfynd/A 14556-2021 artfynd.xlsx
+++ b/artfynd/A 14556-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118365373</v>
+        <v>118365376</v>
       </c>
       <c r="B2" t="n">
-        <v>78484</v>
+        <v>96808</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -781,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118365376</v>
+        <v>118365373</v>
       </c>
       <c r="B3" t="n">
-        <v>96801</v>
+        <v>78491</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,31 +794,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
